--- a/output/roomself_excel/3682.xlsx
+++ b/output/roomself_excel/3682.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>185475</v>
+        <v>154660</v>
       </c>
       <c r="D2" t="n">
-        <v>3712</v>
+        <v>3152</v>
       </c>
       <c r="E2" t="n">
-        <v>507</v>
+        <v>418</v>
       </c>
       <c r="F2" t="n">
-        <v>399</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4760</v>
+        <v>111805</v>
       </c>
       <c r="D3" t="n">
-        <v>564</v>
+        <v>2696</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>154660</v>
+        <v>290636</v>
       </c>
       <c r="D4" t="n">
-        <v>3152</v>
+        <v>4380</v>
       </c>
       <c r="E4" t="n">
-        <v>418</v>
+        <v>660</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250978</v>
+        <v>185475</v>
       </c>
       <c r="D5" t="n">
-        <v>4124</v>
+        <v>3712</v>
       </c>
       <c r="E5" t="n">
-        <v>654</v>
+        <v>507</v>
       </c>
       <c r="F5" t="n">
-        <v>411</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>111574</v>
+        <v>250978</v>
       </c>
       <c r="D6" t="n">
-        <v>4064</v>
+        <v>4124</v>
       </c>
       <c r="E6" t="n">
-        <v>854</v>
+        <v>654</v>
       </c>
       <c r="F6" t="n">
-        <v>198</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>111805</v>
+        <v>146230</v>
       </c>
       <c r="D8" t="n">
-        <v>2696</v>
+        <v>3544</v>
       </c>
       <c r="E8" t="n">
-        <v>475</v>
+        <v>547</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4592</v>
+        <v>81366</v>
       </c>
       <c r="D9" t="n">
-        <v>552</v>
+        <v>2468</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>256815</v>
+        <v>87492</v>
       </c>
       <c r="D10" t="n">
-        <v>4096</v>
+        <v>2372</v>
       </c>
       <c r="E10" t="n">
-        <v>585</v>
+        <v>317</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4345</v>
+        <v>94334</v>
       </c>
       <c r="D11" t="n">
-        <v>536</v>
+        <v>2676</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16480</v>
+        <v>377568</v>
       </c>
       <c r="D12" t="n">
-        <v>1052</v>
+        <v>5204</v>
       </c>
       <c r="E12" t="n">
-        <v>486</v>
+        <v>705</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88879</v>
+        <v>26664</v>
       </c>
       <c r="D13" t="n">
-        <v>2720</v>
+        <v>1336</v>
       </c>
       <c r="E13" t="n">
-        <v>582</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>339</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4840</v>
+        <v>29694</v>
       </c>
       <c r="D14" t="n">
-        <v>572</v>
+        <v>1396</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23452</v>
+        <v>87237</v>
       </c>
       <c r="D15" t="n">
-        <v>1348</v>
+        <v>2408</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88371</v>
+        <v>4760</v>
       </c>
       <c r="D16" t="n">
-        <v>3004</v>
+        <v>564</v>
       </c>
       <c r="E16" t="n">
-        <v>434</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>290636</v>
+        <v>111574</v>
       </c>
       <c r="D17" t="n">
-        <v>4380</v>
+        <v>4064</v>
       </c>
       <c r="E17" t="n">
-        <v>993</v>
+        <v>854</v>
       </c>
       <c r="F17" t="n">
-        <v>660</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3542</v>
+        <v>4592</v>
       </c>
       <c r="D18" t="n">
-        <v>492</v>
+        <v>552</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2660</v>
+        <v>256815</v>
       </c>
       <c r="D19" t="n">
-        <v>444</v>
+        <v>4096</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>102971</v>
+        <v>4345</v>
       </c>
       <c r="D20" t="n">
-        <v>3328</v>
+        <v>536</v>
       </c>
       <c r="E20" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>114874</v>
+        <v>16480</v>
       </c>
       <c r="D21" t="n">
-        <v>3824</v>
+        <v>1052</v>
       </c>
       <c r="E21" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>159551</v>
+        <v>88879</v>
       </c>
       <c r="D22" t="n">
-        <v>4608</v>
+        <v>2720</v>
       </c>
       <c r="E22" t="n">
-        <v>1009</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
-        <v>179</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4930</v>
+        <v>4840</v>
       </c>
       <c r="D23" t="n">
         <v>572</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11475</v>
+        <v>23452</v>
       </c>
       <c r="D24" t="n">
-        <v>880</v>
+        <v>1348</v>
       </c>
       <c r="E24" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>146230</v>
+        <v>88371</v>
       </c>
       <c r="D25" t="n">
-        <v>3544</v>
+        <v>3004</v>
       </c>
       <c r="E25" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>87492</v>
+        <v>3542</v>
       </c>
       <c r="D26" t="n">
-        <v>2372</v>
+        <v>492</v>
       </c>
       <c r="E26" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>74720</v>
+        <v>2660</v>
       </c>
       <c r="D27" t="n">
-        <v>2508</v>
+        <v>444</v>
       </c>
       <c r="E27" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>94334</v>
+        <v>102971</v>
       </c>
       <c r="D28" t="n">
-        <v>2676</v>
+        <v>3328</v>
       </c>
       <c r="E28" t="n">
-        <v>483</v>
+        <v>351</v>
       </c>
       <c r="F28" t="n">
-        <v>218</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>81366</v>
+        <v>114874</v>
       </c>
       <c r="D29" t="n">
-        <v>2468</v>
+        <v>3824</v>
       </c>
       <c r="E29" t="n">
-        <v>191</v>
+        <v>411</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>55475</v>
+        <v>159551</v>
       </c>
       <c r="D30" t="n">
-        <v>1968</v>
+        <v>4608</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>377568</v>
+        <v>4930</v>
       </c>
       <c r="D31" t="n">
-        <v>5204</v>
+        <v>572</v>
       </c>
       <c r="E31" t="n">
-        <v>1290</v>
+        <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>952</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>47200</v>
+        <v>11475</v>
       </c>
       <c r="D32" t="n">
-        <v>1820</v>
+        <v>880</v>
       </c>
       <c r="E32" t="n">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26664</v>
+        <v>74720</v>
       </c>
       <c r="D33" t="n">
-        <v>1336</v>
+        <v>2508</v>
       </c>
       <c r="E33" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="F33" t="n">
         <v>16</v>
@@ -1170,20 +1170,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29694</v>
+        <v>55475</v>
       </c>
       <c r="D34" t="n">
-        <v>1396</v>
+        <v>1968</v>
       </c>
       <c r="E34" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47628</v>
+        <v>47200</v>
       </c>
       <c r="D35" t="n">
-        <v>2016</v>
+        <v>1820</v>
       </c>
       <c r="E35" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1214,20 +1214,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>87237</v>
+        <v>47628</v>
       </c>
       <c r="D36" t="n">
-        <v>2408</v>
+        <v>2016</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3682.xlsx
+++ b/output/roomself_excel/3682.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>3152</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>418</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>17</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,15 @@
       <c r="D3" t="n">
         <v>2696</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +568,31 @@
       <c r="D4" t="n">
         <v>4380</v>
       </c>
-      <c r="E4" t="n">
-        <v>660</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>643</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +609,31 @@
       <c r="D5" t="n">
         <v>3712</v>
       </c>
-      <c r="E5" t="n">
-        <v>507</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>382</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>490</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +650,31 @@
       <c r="D6" t="n">
         <v>4124</v>
       </c>
-      <c r="E6" t="n">
-        <v>654</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>411</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>637</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,31 @@
       <c r="D7" t="n">
         <v>4036</v>
       </c>
-      <c r="E7" t="n">
-        <v>629</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>416</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>611</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +732,31 @@
       <c r="D8" t="n">
         <v>3544</v>
       </c>
-      <c r="E8" t="n">
-        <v>547</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>276</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>260</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +773,23 @@
       <c r="D9" t="n">
         <v>2468</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>191</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>16</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +806,23 @@
       <c r="D10" t="n">
         <v>2372</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>317</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>16</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +839,31 @@
       <c r="D11" t="n">
         <v>2676</v>
       </c>
-      <c r="E11" t="n">
-        <v>483</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>218</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>467</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +880,31 @@
       <c r="D12" t="n">
         <v>5204</v>
       </c>
-      <c r="E12" t="n">
-        <v>705</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>453</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>689</v>
+      </c>
+      <c r="J12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,23 @@
       <c r="D13" t="n">
         <v>1336</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>132</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>16</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +954,23 @@
       <c r="D14" t="n">
         <v>1396</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>147</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>16</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +987,15 @@
       <c r="D15" t="n">
         <v>2408</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1012,23 @@
       <c r="D16" t="n">
         <v>564</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>56</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>17</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1045,31 @@
       <c r="D17" t="n">
         <v>4064</v>
       </c>
-      <c r="E17" t="n">
-        <v>854</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>198</v>
-      </c>
+        <v>836</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>180</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1086,15 @@
       <c r="D18" t="n">
         <v>552</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1111,23 @@
       <c r="D19" t="n">
         <v>4096</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>585</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>18</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1144,15 @@
       <c r="D20" t="n">
         <v>536</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1169,15 @@
       <c r="D21" t="n">
         <v>1052</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1194,15 @@
       <c r="D22" t="n">
         <v>2720</v>
       </c>
-      <c r="E22" t="n">
-        <v>120</v>
-      </c>
-      <c r="F22" t="n">
-        <v>18</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1219,15 @@
       <c r="D23" t="n">
         <v>572</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1244,15 @@
       <c r="D24" t="n">
         <v>1348</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1269,15 @@
       <c r="D25" t="n">
         <v>3004</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1294,15 @@
       <c r="D26" t="n">
         <v>492</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1319,15 @@
       <c r="D27" t="n">
         <v>444</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1344,31 @@
       <c r="D28" t="n">
         <v>3328</v>
       </c>
-      <c r="E28" t="n">
-        <v>351</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>279</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="G28" t="n">
+        <v>18</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>243</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,11 +1385,38 @@
       <c r="D29" t="n">
         <v>3824</v>
       </c>
-      <c r="E29" t="n">
-        <v>411</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>321</v>
+        <v>304</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>376</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1091,12 +1434,31 @@
       <c r="D30" t="n">
         <v>4608</v>
       </c>
-      <c r="E30" t="n">
-        <v>1009</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>179</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G30" t="n">
+        <v>18</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>991</v>
+      </c>
+      <c r="J30" t="n">
+        <v>18</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1475,31 @@
       <c r="D31" t="n">
         <v>572</v>
       </c>
-      <c r="E31" t="n">
-        <v>58</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="n">
         <v>17</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1516,23 @@
       <c r="D32" t="n">
         <v>880</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>135</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>17</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1549,23 @@
       <c r="D33" t="n">
         <v>2508</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>160</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>16</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1582,15 @@
       <c r="D34" t="n">
         <v>1968</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1607,15 @@
       <c r="D35" t="n">
         <v>1820</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1632,31 @@
       <c r="D36" t="n">
         <v>2016</v>
       </c>
-      <c r="E36" t="n">
-        <v>226</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>142</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G36" t="n">
+        <v>16</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>210</v>
+      </c>
+      <c r="J36" t="n">
+        <v>16</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3682.xlsx
+++ b/output/roomself_excel/3682.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,46 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -527,6 +567,26 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -552,6 +612,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +661,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -634,6 +722,38 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>203</v>
+      </c>
+      <c r="U5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -675,6 +795,38 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>17</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>200</v>
+      </c>
+      <c r="U6" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -716,6 +868,26 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -757,6 +929,38 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>104</v>
+      </c>
+      <c r="U8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -790,6 +994,26 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -823,6 +1047,26 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -864,6 +1108,26 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -905,6 +1169,38 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>182</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -938,6 +1234,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -971,6 +1275,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -996,6 +1308,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1029,6 +1349,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1070,6 +1398,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1095,6 +1431,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1128,6 +1472,26 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>258</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>18</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1153,6 +1517,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1178,6 +1550,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1203,6 +1583,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1228,6 +1616,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1253,6 +1649,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1278,6 +1682,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1303,6 +1715,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1328,6 +1748,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1369,6 +1797,26 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>18</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1418,6 +1866,26 @@
       <c r="M29" t="n">
         <v>16</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>17</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1459,6 +1927,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1500,6 +1976,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1533,6 +2017,26 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>17</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1566,6 +2070,26 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>16</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1591,6 +2115,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1616,6 +2148,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1657,6 +2197,26 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>16</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
